--- a/outputs/daily/hr_rankings_2026-08-15.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-15.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ180"/>
+  <dimension ref="A1:BZ181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4128,28 +4128,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4758,34 +4762,30 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6648,28 +6648,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14994,34 +14998,30 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC46" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD46" t="inlineStr"/>
       <c r="AE46" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -23062,34 +23062,30 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC71" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD71" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AD71" t="inlineStr"/>
       <c r="AE71" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -25268,34 +25264,30 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC78" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD78" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AD78" t="inlineStr"/>
       <c r="AE78" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -26532,34 +26524,30 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC82" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD82" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AD82" t="inlineStr"/>
       <c r="AE82" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -41804,34 +41792,30 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA130" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC130" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD130" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD130" t="inlineStr"/>
       <c r="AE130" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -48955,27 +48939,27 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>807712</t>
+          <t>680716</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Luke Keaschall</t>
+          <t>Jonathan Ornelas</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-08-15T23:10:00Z</t>
+          <t>2026-08-15T23:15:00Z</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -48985,17 +48969,17 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Jesús Luzardo</t>
+          <t>Justin Wrobleski</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>666200</t>
+          <t>680736</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -49004,7 +48988,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>38.8</v>
+        <v>39</v>
       </c>
       <c r="M153" t="inlineStr">
         <is>
@@ -49022,22 +49006,22 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>11.3</v>
+        <v>12</v>
       </c>
       <c r="Q153" t="n">
-        <v>20.8</v>
+        <v>45</v>
       </c>
       <c r="R153" t="n">
-        <v>62.6</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="S153" t="n">
-        <v>76.2</v>
+        <v>44.8</v>
       </c>
       <c r="T153" t="n">
         <v>78</v>
       </c>
       <c r="U153" t="n">
-        <v>48.1</v>
+        <v>7</v>
       </c>
       <c r="V153" t="n">
         <v>50</v>
@@ -49055,7 +49039,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -49088,32 +49072,32 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AL153" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/22, 1 HR</t>
+          <t>Last 6 games: 2/12, 0 HR</t>
         </is>
       </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.1% barrel, 13.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.4% barrel, 13.7 HR allowed</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
@@ -49123,102 +49107,102 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ153" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AR153" t="inlineStr">
         <is>
-          <t>85.15</t>
+          <t>86.24</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>96.6715</t>
+          <t>97.2612</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr">
         <is>
-          <t>0.3563</t>
+          <t>0.1434</t>
         </is>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>0.1104</t>
+          <t>0.0155</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>0.3142</t>
+          <t>0.1668</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>68.64</t>
+          <t>72.44</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>29.54</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>39.31</t>
+          <t>47.01</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>0.1164</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="BD153" t="inlineStr">
         <is>
-          <t>32.83</t>
+          <t>44.51</t>
         </is>
       </c>
       <c r="BE153" t="inlineStr">
         <is>
-          <t>87.45</t>
+          <t>90.46</t>
         </is>
       </c>
       <c r="BF153" t="inlineStr">
         <is>
-          <t>0.3172</t>
+          <t>0.4192</t>
         </is>
       </c>
       <c r="BG153" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t>0.157</t>
         </is>
       </c>
       <c r="BH153" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="BI153" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ153" t="inlineStr">
@@ -49228,27 +49212,27 @@
       </c>
       <c r="BK153" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
         </is>
       </c>
       <c r="BL153" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>62</t>
         </is>
       </c>
       <c r="BM153" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN153" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BO153" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BP153" t="inlineStr"/>
@@ -49269,12 +49253,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>686797</t>
+          <t>807712</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Luke Keaschall</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -49299,7 +49283,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -49318,7 +49302,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>38.7</v>
+        <v>38.8</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
@@ -49336,22 +49320,22 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>18.3</v>
+        <v>11.3</v>
       </c>
       <c r="Q154" t="n">
-        <v>19.4</v>
+        <v>20.8</v>
       </c>
       <c r="R154" t="n">
         <v>62.6</v>
       </c>
       <c r="S154" t="n">
-        <v>64.3</v>
+        <v>76.2</v>
       </c>
       <c r="T154" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U154" t="n">
-        <v>46.9</v>
+        <v>48.1</v>
       </c>
       <c r="V154" t="n">
         <v>50</v>
@@ -49369,7 +49353,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -49407,12 +49391,12 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL154" t="inlineStr">
@@ -49422,12 +49406,12 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>Last 7 games: 9/29, 1 HR</t>
+          <t>Last 7 games: 7/22, 1 HR</t>
         </is>
       </c>
       <c r="AN154" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.1% barrel, 13.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.1% barrel, 13.2 HR allowed</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -49437,67 +49421,67 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AQ154" t="inlineStr">
         <is>
-          <t>33.81</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="AR154" t="inlineStr">
         <is>
-          <t>87.97</t>
+          <t>85.15</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr">
         <is>
-          <t>97.4122</t>
+          <t>96.6715</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr">
         <is>
-          <t>0.3425</t>
+          <t>0.3563</t>
         </is>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>0.1155</t>
+          <t>0.1104</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>0.2764</t>
+          <t>0.3142</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>68.64</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>42.48</t>
+          <t>39.31</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>0.1627</t>
+          <t>0.1164</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
@@ -49583,22 +49567,22 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>666023</t>
+          <t>686797</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Freddy Fermin</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -49613,17 +49597,17 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Joey Cantillo</t>
+          <t>Jesús Luzardo</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>676282</t>
+          <t>666200</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -49632,7 +49616,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>38.5</v>
+        <v>38.7</v>
       </c>
       <c r="M155" t="inlineStr">
         <is>
@@ -49650,22 +49634,22 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>15.3</v>
+        <v>18.3</v>
       </c>
       <c r="Q155" t="n">
-        <v>38.6</v>
+        <v>19.4</v>
       </c>
       <c r="R155" t="n">
-        <v>50.1</v>
+        <v>62.6</v>
       </c>
       <c r="S155" t="n">
-        <v>44.8</v>
+        <v>64.3</v>
       </c>
       <c r="T155" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U155" t="n">
-        <v>57.5</v>
+        <v>46.9</v>
       </c>
       <c r="V155" t="n">
         <v>50</v>
@@ -49683,7 +49667,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -49721,12 +49705,12 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL155" t="inlineStr">
@@ -49736,12 +49720,12 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>Contact streak: 8/21 over last 7 games</t>
+          <t>Last 7 games: 9/29, 1 HR</t>
         </is>
       </c>
       <c r="AN155" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.1% barrel, 13.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.1% barrel, 13.2 HR allowed</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
@@ -49751,102 +49735,102 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AQ155" t="inlineStr">
         <is>
-          <t>29.69</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="AR155" t="inlineStr">
         <is>
-          <t>88.05</t>
+          <t>87.97</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr">
         <is>
-          <t>97.1872</t>
+          <t>97.4122</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr">
         <is>
-          <t>0.3217</t>
+          <t>0.3425</t>
         </is>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>0.1058</t>
+          <t>0.1155</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2764</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>69.78</t>
+          <t>69.92</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>42.48</t>
+        </is>
+      </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>28.02</t>
+        </is>
+      </c>
+      <c r="BA155" t="inlineStr">
+        <is>
+          <t>16.7</t>
+        </is>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>0.1627</t>
+        </is>
+      </c>
+      <c r="BC155" t="inlineStr">
+        <is>
           <t>6.07</t>
         </is>
       </c>
-      <c r="AY155" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="AZ155" t="inlineStr">
-        <is>
-          <t>28.77</t>
-        </is>
-      </c>
-      <c r="BA155" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="BB155" t="inlineStr">
-        <is>
-          <t>0.1125</t>
-        </is>
-      </c>
-      <c r="BC155" t="inlineStr">
-        <is>
-          <t>8.11</t>
-        </is>
-      </c>
       <c r="BD155" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>32.83</t>
         </is>
       </c>
       <c r="BE155" t="inlineStr">
         <is>
-          <t>88.73</t>
+          <t>87.45</t>
         </is>
       </c>
       <c r="BF155" t="inlineStr">
         <is>
-          <t>0.3756</t>
+          <t>0.3172</t>
         </is>
       </c>
       <c r="BG155" t="inlineStr">
         <is>
-          <t>0.1438</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="BH155" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="BI155" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ155" t="inlineStr">
@@ -49856,27 +49840,27 @@
       </c>
       <c r="BK155" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=41.4962&amp;lon=-81.6852</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
         </is>
       </c>
       <c r="BL155" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BM155" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="BN155" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BO155" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BP155" t="inlineStr"/>
@@ -49897,27 +49881,27 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>666023</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Freddy Fermin</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-08-15T22:10:00Z</t>
+          <t>2026-08-15T23:10:00Z</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -49927,26 +49911,26 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Joey Cantillo</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>680694</t>
+          <t>676282</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>38.3</v>
+        <v>38.5</v>
       </c>
       <c r="M156" t="inlineStr">
         <is>
@@ -49960,26 +49944,26 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P156" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="Q156" t="n">
-        <v>34</v>
+        <v>38.6</v>
       </c>
       <c r="R156" t="n">
-        <v>48.1</v>
+        <v>50.1</v>
       </c>
       <c r="S156" t="n">
-        <v>76.2</v>
+        <v>44.8</v>
       </c>
       <c r="T156" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U156" t="n">
-        <v>50.3</v>
+        <v>57.5</v>
       </c>
       <c r="V156" t="n">
         <v>50</v>
@@ -49997,7 +49981,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -50040,7 +50024,7 @@
       </c>
       <c r="AK156" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL156" t="inlineStr">
@@ -50050,12 +50034,12 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Contact streak: 8/21 over last 7 games</t>
         </is>
       </c>
       <c r="AN156" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 10.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.1% barrel, 13.5 HR allowed</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -50065,102 +50049,102 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AQ156" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>29.69</t>
         </is>
       </c>
       <c r="AR156" t="inlineStr">
         <is>
-          <t>85.25</t>
+          <t>88.05</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr">
         <is>
-          <t>97.3292</t>
+          <t>97.1872</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr">
         <is>
-          <t>0.3563</t>
+          <t>0.3217</t>
         </is>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>0.1047</t>
+          <t>0.1058</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>0.2796</t>
+          <t>0.2721</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>73.03</t>
+          <t>69.78</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>0.1622</t>
+          <t>0.1125</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="BD156" t="inlineStr">
         <is>
-          <t>37.71</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BE156" t="inlineStr">
         <is>
-          <t>88.47</t>
+          <t>88.73</t>
         </is>
       </c>
       <c r="BF156" t="inlineStr">
         <is>
-          <t>0.3634</t>
+          <t>0.3756</t>
         </is>
       </c>
       <c r="BG156" t="inlineStr">
         <is>
-          <t>0.1366</t>
+          <t>0.1438</t>
         </is>
       </c>
       <c r="BH156" t="inlineStr">
         <is>
-          <t>22.94</t>
+          <t>27.37</t>
         </is>
       </c>
       <c r="BI156" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ156" t="inlineStr">
@@ -50170,27 +50154,27 @@
       </c>
       <c r="BK156" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=27.7682&amp;lon=-82.6534</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=41.4962&amp;lon=-81.6852</t>
         </is>
       </c>
       <c r="BL156" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BM156" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN156" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BO156" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BP156" t="inlineStr"/>
@@ -50211,27 +50195,27 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>668952</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Ryan Kreidler</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-08-15T23:10:00Z</t>
+          <t>2026-08-15T22:10:00Z</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -50241,26 +50225,26 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Jesús Luzardo</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>666200</t>
+          <t>680694</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>38</v>
+        <v>38.3</v>
       </c>
       <c r="M157" t="inlineStr">
         <is>
@@ -50274,26 +50258,26 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P157" t="n">
-        <v>25.4</v>
+        <v>13.2</v>
       </c>
       <c r="Q157" t="n">
-        <v>20.8</v>
+        <v>34</v>
       </c>
       <c r="R157" t="n">
-        <v>62.6</v>
+        <v>48.1</v>
       </c>
       <c r="S157" t="n">
-        <v>52.4</v>
+        <v>76.2</v>
       </c>
       <c r="T157" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U157" t="n">
-        <v>10.6</v>
+        <v>50.3</v>
       </c>
       <c r="V157" t="n">
         <v>50</v>
@@ -50311,7 +50295,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -50349,27 +50333,27 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL157" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AN157" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.1% barrel, 13.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -50379,102 +50363,102 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AQ157" t="inlineStr">
         <is>
-          <t>33.85</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="AR157" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.25</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr">
         <is>
-          <t>99.1033</t>
+          <t>97.3292</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.3563</t>
         </is>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>0.1322</t>
+          <t>0.1047</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>0.2731</t>
+          <t>0.2796</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>73.03</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>32.16</t>
+          <t>31.18</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>0.1022</t>
+          <t>0.1622</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="BD157" t="inlineStr">
         <is>
-          <t>32.83</t>
+          <t>37.71</t>
         </is>
       </c>
       <c r="BE157" t="inlineStr">
         <is>
-          <t>87.45</t>
+          <t>88.47</t>
         </is>
       </c>
       <c r="BF157" t="inlineStr">
         <is>
-          <t>0.3172</t>
+          <t>0.3634</t>
         </is>
       </c>
       <c r="BG157" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t>0.1366</t>
         </is>
       </c>
       <c r="BH157" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>22.94</t>
         </is>
       </c>
       <c r="BI157" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ157" t="inlineStr">
@@ -50484,27 +50468,27 @@
       </c>
       <c r="BK157" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=27.7682&amp;lon=-82.6534</t>
         </is>
       </c>
       <c r="BL157" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BM157" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>34</t>
         </is>
       </c>
       <c r="BN157" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BO157" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BP157" t="inlineStr"/>
@@ -50525,27 +50509,27 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>668952</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Ryan Kreidler</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-08-15T22:10:00Z</t>
+          <t>2026-08-15T23:10:00Z</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -50555,26 +50539,26 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Jesús Luzardo</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>680694</t>
+          <t>666200</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>37.7</v>
+        <v>38</v>
       </c>
       <c r="M158" t="inlineStr">
         <is>
@@ -50592,22 +50576,22 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>0.3</v>
+        <v>25.4</v>
       </c>
       <c r="Q158" t="n">
-        <v>34</v>
+        <v>20.8</v>
       </c>
       <c r="R158" t="n">
-        <v>48.1</v>
+        <v>62.6</v>
       </c>
       <c r="S158" t="n">
-        <v>86.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T158" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U158" t="n">
-        <v>42</v>
+        <v>10.6</v>
       </c>
       <c r="V158" t="n">
         <v>50</v>
@@ -50625,7 +50609,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -50663,12 +50647,12 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL158" t="inlineStr">
@@ -50678,12 +50662,12 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>Contact streak: 12/30 over last 7 games</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AN158" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 10.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.1% barrel, 13.2 HR allowed</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -50693,102 +50677,102 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AQ158" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="AR158" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr">
         <is>
-          <t>92.9205</t>
+          <t>99.1033</t>
         </is>
       </c>
       <c r="AT158" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>0.0389</t>
+          <t>0.1322</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>0.2753</t>
+          <t>0.2731</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>64.66</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>32.16</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>27.71</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>0.0549</t>
+          <t>0.1022</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BD158" t="inlineStr">
         <is>
-          <t>37.71</t>
+          <t>32.83</t>
         </is>
       </c>
       <c r="BE158" t="inlineStr">
         <is>
-          <t>88.47</t>
+          <t>87.45</t>
         </is>
       </c>
       <c r="BF158" t="inlineStr">
         <is>
-          <t>0.3634</t>
+          <t>0.3172</t>
         </is>
       </c>
       <c r="BG158" t="inlineStr">
         <is>
-          <t>0.1366</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="BH158" t="inlineStr">
         <is>
-          <t>22.94</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="BI158" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ158" t="inlineStr">
@@ -50798,27 +50782,27 @@
       </c>
       <c r="BK158" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=27.7682&amp;lon=-82.6534</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
         </is>
       </c>
       <c r="BL158" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BM158" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>16</t>
         </is>
       </c>
       <c r="BN158" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BO158" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BP158" t="inlineStr"/>
@@ -50839,12 +50823,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -50869,7 +50853,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -50906,7 +50890,7 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>15.1</v>
+        <v>0.3</v>
       </c>
       <c r="Q159" t="n">
         <v>34</v>
@@ -50915,13 +50899,13 @@
         <v>48.1</v>
       </c>
       <c r="S159" t="n">
-        <v>52.4</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T159" t="n">
         <v>80</v>
       </c>
       <c r="U159" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="V159" t="n">
         <v>50</v>
@@ -50939,7 +50923,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -50977,12 +50961,12 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AL159" t="inlineStr">
@@ -50992,7 +50976,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>Contact streak: 8/18 over last 7 games</t>
+          <t>Contact streak: 12/30 over last 7 games</t>
         </is>
       </c>
       <c r="AN159" t="inlineStr">
@@ -51007,67 +50991,67 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ159" t="inlineStr">
         <is>
-          <t>32.69</t>
+          <t>14.64</t>
         </is>
       </c>
       <c r="AR159" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr">
         <is>
-          <t>96.9541</t>
+          <t>92.9205</t>
         </is>
       </c>
       <c r="AT159" t="inlineStr">
         <is>
-          <t>0.3667</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>0.1011</t>
+          <t>0.0389</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.2753</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>64.66</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>27.71</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>21.19</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>0.1162</t>
+          <t>0.0549</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
@@ -51153,27 +51137,27 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>655316</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Andruw Monasterio</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-08-15T23:15:00Z</t>
+          <t>2026-08-15T22:10:00Z</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -51188,12 +51172,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Jared Jones</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>683003</t>
+          <t>680694</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -51202,7 +51186,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>36.7</v>
+        <v>37.7</v>
       </c>
       <c r="M160" t="inlineStr">
         <is>
@@ -51216,26 +51200,26 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P160" t="n">
-        <v>26.4</v>
+        <v>15.1</v>
       </c>
       <c r="Q160" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="R160" t="n">
-        <v>32.3</v>
+        <v>48.1</v>
       </c>
       <c r="S160" t="n">
         <v>52.4</v>
       </c>
       <c r="T160" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U160" t="n">
-        <v>19.5</v>
+        <v>45</v>
       </c>
       <c r="V160" t="n">
         <v>50</v>
@@ -51274,7 +51258,7 @@
       <c r="AD160" t="inlineStr"/>
       <c r="AE160" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF160" t="inlineStr"/>
@@ -51291,12 +51275,12 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AL160" t="inlineStr">
@@ -51306,12 +51290,12 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Contact streak: 8/18 over last 7 games</t>
         </is>
       </c>
       <c r="AN160" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 10.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
@@ -51321,102 +51305,102 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AQ160" t="inlineStr">
         <is>
-          <t>34.47</t>
+          <t>32.69</t>
         </is>
       </c>
       <c r="AR160" t="inlineStr">
         <is>
-          <t>87.98</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr">
         <is>
-          <t>97.7733</t>
+          <t>96.9541</t>
         </is>
       </c>
       <c r="AT160" t="inlineStr">
         <is>
-          <t>0.3833</t>
+          <t>0.3667</t>
         </is>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>0.1418</t>
+          <t>0.1011</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>0.3031</t>
+          <t>0.325</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>69.24</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>32.04</t>
+          <t>21.19</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1162</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="BD160" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>37.71</t>
         </is>
       </c>
       <c r="BE160" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.47</t>
         </is>
       </c>
       <c r="BF160" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>0.3634</t>
         </is>
       </c>
       <c r="BG160" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.1366</t>
         </is>
       </c>
       <c r="BH160" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>22.94</t>
         </is>
       </c>
       <c r="BI160" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ160" t="inlineStr">
@@ -51426,27 +51410,27 @@
       </c>
       <c r="BK160" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=40.4469&amp;lon=-80.0057</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=27.7682&amp;lon=-82.6534</t>
         </is>
       </c>
       <c r="BL160" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BM160" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
       <c r="BN160" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BO160" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BP160" t="inlineStr"/>
@@ -51467,47 +51451,47 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>677649</t>
+          <t>655316</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Ezequiel Duran</t>
+          <t>Andruw Monasterio</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-16T01:40:00Z</t>
+          <t>2026-08-15T23:15:00Z</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>J.T. Ginn</t>
+          <t>Jared Jones</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>669372</t>
+          <t>683003</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -51516,7 +51500,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>36.5</v>
+        <v>36.7</v>
       </c>
       <c r="M161" t="inlineStr">
         <is>
@@ -51530,26 +51514,26 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P161" t="n">
-        <v>20.4</v>
+        <v>26.4</v>
       </c>
       <c r="Q161" t="n">
-        <v>30.2</v>
+        <v>40</v>
       </c>
       <c r="R161" t="n">
-        <v>56.4</v>
+        <v>32.3</v>
       </c>
       <c r="S161" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T161" t="n">
         <v>50</v>
       </c>
       <c r="U161" t="n">
-        <v>9.800000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="V161" t="n">
         <v>50</v>
@@ -51557,42 +51541,38 @@
       <c r="W161" t="inlineStr"/>
       <c r="X161" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y161" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA161" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD161" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD161" t="inlineStr"/>
       <c r="AE161" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF161" t="inlineStr"/>
@@ -51614,7 +51594,7 @@
       </c>
       <c r="AK161" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL161" t="inlineStr">
@@ -51624,12 +51604,12 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AN161" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 14.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
@@ -51639,102 +51619,102 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="AQ161" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>34.47</t>
         </is>
       </c>
       <c r="AR161" t="inlineStr">
         <is>
-          <t>87.68</t>
+          <t>87.98</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr">
         <is>
-          <t>98.7601</t>
+          <t>97.7733</t>
         </is>
       </c>
       <c r="AT161" t="inlineStr">
         <is>
-          <t>0.3552</t>
+          <t>0.3833</t>
         </is>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.1418</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>0.2869</t>
+          <t>0.3031</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>72.34</t>
+          <t>69.24</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>24.52</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>35.73</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>21.51</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>0.1418</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BD161" t="inlineStr">
         <is>
-          <t>37.64</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="BE161" t="inlineStr">
         <is>
-          <t>87.49</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="BF161" t="inlineStr">
         <is>
-          <t>0.3677</t>
+          <t>0.387</t>
         </is>
       </c>
       <c r="BG161" t="inlineStr">
         <is>
-          <t>0.1344</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="BH161" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="BI161" t="inlineStr">
         <is>
-          <t>214 deg</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BJ161" t="inlineStr">
@@ -51744,12 +51724,12 @@
       </c>
       <c r="BK161" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=40.4469&amp;lon=-80.0057</t>
         </is>
       </c>
       <c r="BL161" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>87</t>
         </is>
       </c>
       <c r="BM161" t="inlineStr">
@@ -51759,12 +51739,12 @@
       </c>
       <c r="BN161" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BO161" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BP161" t="inlineStr"/>
@@ -51785,12 +51765,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>553869</t>
+          <t>677649</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Elias Diaz</t>
+          <t>Ezequiel Duran</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -51815,7 +51795,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -51852,7 +51832,7 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>25.6</v>
+        <v>20.4</v>
       </c>
       <c r="Q162" t="n">
         <v>30.2</v>
@@ -51861,13 +51841,13 @@
         <v>56.4</v>
       </c>
       <c r="S162" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T162" t="n">
         <v>50</v>
       </c>
       <c r="U162" t="n">
-        <v>9.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V162" t="n">
         <v>50</v>
@@ -51885,7 +51865,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -51927,12 +51907,12 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL162" t="inlineStr">
@@ -51942,7 +51922,7 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 0 HR</t>
+          <t>Last 7 games: 5/27, 0 HR</t>
         </is>
       </c>
       <c r="AN162" t="inlineStr">
@@ -51957,67 +51937,67 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AQ162" t="inlineStr">
         <is>
-          <t>37.72</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AR162" t="inlineStr">
         <is>
-          <t>87.21</t>
+          <t>87.68</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr">
         <is>
-          <t>99.6402</t>
+          <t>98.7601</t>
         </is>
       </c>
       <c r="AT162" t="inlineStr">
         <is>
-          <t>0.3459</t>
+          <t>0.3552</t>
         </is>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>0.1264</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>0.2617</t>
+          <t>0.2869</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>74.34</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>24.52</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>37.72</t>
+          <t>35.73</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>0.1515</t>
+          <t>0.1418</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
@@ -52103,24 +52083,24 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>675961</t>
+          <t>553869</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Alika Williams</t>
+          <t>Elias Diaz</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
           <t>ATH</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
       <c r="F163" t="inlineStr">
         <is>
           <t>2026-08-16T01:40:00Z</t>
@@ -52133,22 +52113,22 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>MacKenzie Gore</t>
+          <t>J.T. Ginn</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>669022</t>
+          <t>669372</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L163" t="n">
@@ -52166,26 +52146,26 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P163" t="n">
-        <v>8.5</v>
+        <v>25.6</v>
       </c>
       <c r="Q163" t="n">
-        <v>46.8</v>
+        <v>30.2</v>
       </c>
       <c r="R163" t="n">
         <v>56.4</v>
       </c>
       <c r="S163" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T163" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U163" t="n">
-        <v>16.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V163" t="n">
         <v>50</v>
@@ -52203,7 +52183,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -52228,7 +52208,7 @@
       </c>
       <c r="AE163" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF163" t="inlineStr"/>
@@ -52245,12 +52225,12 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL163" t="inlineStr">
@@ -52260,12 +52240,12 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/13, 0 HR</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AN163" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.5% barrel, 17.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 14.2 HR allowed</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
@@ -52275,97 +52255,97 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="AQ163" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>37.72</t>
         </is>
       </c>
       <c r="AR163" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>87.21</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr">
         <is>
-          <t>97.3169</t>
+          <t>99.6402</t>
         </is>
       </c>
       <c r="AT163" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>0.3459</t>
         </is>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.1264</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>0.2617</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>74.34</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>37.72</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>28.15</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.1515</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BD163" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>37.64</t>
         </is>
       </c>
       <c r="BE163" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>87.49</t>
         </is>
       </c>
       <c r="BF163" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>0.3677</t>
         </is>
       </c>
       <c r="BG163" t="inlineStr">
         <is>
-          <t>0.1523</t>
+          <t>0.1344</t>
         </is>
       </c>
       <c r="BH163" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="BI163" t="inlineStr">
@@ -52421,47 +52401,47 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>675961</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Alika Williams</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-08-15T23:10:00Z</t>
+          <t>2026-08-16T01:40:00Z</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Wandy Peralta</t>
+          <t>MacKenzie Gore</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>593974</t>
+          <t>669022</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -52470,7 +52450,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>36.1</v>
+        <v>36.5</v>
       </c>
       <c r="M164" t="inlineStr">
         <is>
@@ -52484,26 +52464,26 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P164" t="n">
-        <v>29.6</v>
+        <v>8.5</v>
       </c>
       <c r="Q164" t="n">
-        <v>17.5</v>
+        <v>46.8</v>
       </c>
       <c r="R164" t="n">
-        <v>50.1</v>
+        <v>56.4</v>
       </c>
       <c r="S164" t="n">
-        <v>52.4</v>
+        <v>40.2</v>
       </c>
       <c r="T164" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U164" t="n">
-        <v>0</v>
+        <v>16.6</v>
       </c>
       <c r="V164" t="n">
         <v>50</v>
@@ -52511,38 +52491,42 @@
       <c r="W164" t="inlineStr"/>
       <c r="X164" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y164" t="inlineStr">
+      <c r="AB164" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA164" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AD164" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AD164" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AE164" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF164" t="inlineStr"/>
@@ -52559,12 +52543,12 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AL164" t="inlineStr">
@@ -52574,12 +52558,12 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/20, 0 HR</t>
+          <t>Last 7 games: 3/13, 0 HR</t>
         </is>
       </c>
       <c r="AN164" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 4.6% barrel, 5.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.5% barrel, 17.9 HR allowed</t>
         </is>
       </c>
       <c r="AO164" t="inlineStr">
@@ -52589,102 +52573,102 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AQ164" t="inlineStr">
         <is>
-          <t>38.43</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="AR164" t="inlineStr">
         <is>
-          <t>89.67</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr">
         <is>
-          <t>99.3565</t>
+          <t>97.3169</t>
         </is>
       </c>
       <c r="AT164" t="inlineStr">
         <is>
-          <t>0.3652</t>
+          <t>0.283</t>
         </is>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>0.1426</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>0.2822</t>
+          <t>0.243</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>72.55</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>28.23</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>33.83</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>26.34</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>0.1065</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>9.48</t>
         </is>
       </c>
       <c r="BD164" t="inlineStr">
         <is>
-          <t>33.96</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="BE164" t="inlineStr">
         <is>
-          <t>87.04</t>
+          <t>89.49</t>
         </is>
       </c>
       <c r="BF164" t="inlineStr">
         <is>
-          <t>0.3759</t>
+          <t>0.387</t>
         </is>
       </c>
       <c r="BG164" t="inlineStr">
         <is>
-          <t>0.1169</t>
+          <t>0.1523</t>
         </is>
       </c>
       <c r="BH164" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BI164" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>214 deg</t>
         </is>
       </c>
       <c r="BJ164" t="inlineStr">
@@ -52694,12 +52678,12 @@
       </c>
       <c r="BK164" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=41.4962&amp;lon=-81.6852</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
         </is>
       </c>
       <c r="BL164" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>47</t>
         </is>
       </c>
       <c r="BM164" t="inlineStr">
@@ -52709,12 +52693,12 @@
       </c>
       <c r="BN164" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BO164" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BP164" t="inlineStr"/>
@@ -52735,32 +52719,32 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>686475</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Tyler Tolbert</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-08-16T01:38:00Z</t>
+          <t>2026-08-15T23:10:00Z</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -52770,12 +52754,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Reid Detmers</t>
+          <t>Wandy Peralta</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>672282</t>
+          <t>593974</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -52798,26 +52782,26 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P165" t="n">
-        <v>9.699999999999999</v>
+        <v>29.6</v>
       </c>
       <c r="Q165" t="n">
-        <v>41</v>
+        <v>17.5</v>
       </c>
       <c r="R165" t="n">
-        <v>54.7</v>
+        <v>50.1</v>
       </c>
       <c r="S165" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T165" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U165" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="V165" t="n">
         <v>50</v>
@@ -52825,39 +52809,35 @@
       <c r="W165" t="inlineStr"/>
       <c r="X165" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y165" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA165" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD165" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr"/>
       <c r="AE165" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -52882,7 +52862,7 @@
       </c>
       <c r="AK165" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL165" t="inlineStr">
@@ -52892,12 +52872,12 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/10, 0 HR</t>
+          <t>Last 7 games: 2/20, 0 HR</t>
         </is>
       </c>
       <c r="AN165" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 13.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 4.6% barrel, 5.0 HR allowed</t>
         </is>
       </c>
       <c r="AO165" t="inlineStr">
@@ -52907,102 +52887,102 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AQ165" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>38.43</t>
         </is>
       </c>
       <c r="AR165" t="inlineStr">
         <is>
-          <t>86.13</t>
+          <t>89.67</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr">
         <is>
-          <t>97.085</t>
+          <t>99.3565</t>
         </is>
       </c>
       <c r="AT165" t="inlineStr">
         <is>
-          <t>0.3416</t>
+          <t>0.3652</t>
         </is>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>0.0809</t>
+          <t>0.1426</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>0.3116</t>
+          <t>0.2822</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>69.32</t>
+          <t>72.55</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>28.23</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>35.69</t>
+          <t>33.83</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>26.34</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>0.1392</t>
+          <t>0.1065</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="BD165" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>33.96</t>
         </is>
       </c>
       <c r="BE165" t="inlineStr">
         <is>
-          <t>90.03</t>
+          <t>87.04</t>
         </is>
       </c>
       <c r="BF165" t="inlineStr">
         <is>
-          <t>0.3686</t>
+          <t>0.3759</t>
         </is>
       </c>
       <c r="BG165" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.1169</t>
         </is>
       </c>
       <c r="BH165" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>16.92</t>
         </is>
       </c>
       <c r="BI165" t="inlineStr">
         <is>
-          <t>230 deg</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ165" t="inlineStr">
@@ -53012,12 +52992,12 @@
       </c>
       <c r="BK165" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=41.4962&amp;lon=-81.6852</t>
         </is>
       </c>
       <c r="BL165" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BM165" t="inlineStr">
@@ -53027,12 +53007,12 @@
       </c>
       <c r="BN165" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BO165" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BP165" t="inlineStr"/>
@@ -53053,47 +53033,47 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>701785</t>
+          <t>686475</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Kaelen Culpepper</t>
+          <t>Tyler Tolbert</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-08-15T23:10:00Z</t>
+          <t>2026-08-16T01:38:00Z</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Jesús Luzardo</t>
+          <t>Reid Detmers</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>666200</t>
+          <t>672282</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -53102,7 +53082,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="M166" t="inlineStr">
         <is>
@@ -53116,26 +53096,26 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P166" t="n">
-        <v>19.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q166" t="n">
-        <v>20.8</v>
+        <v>41</v>
       </c>
       <c r="R166" t="n">
-        <v>62.6</v>
+        <v>54.7</v>
       </c>
       <c r="S166" t="n">
-        <v>44.8</v>
+        <v>47.9</v>
       </c>
       <c r="T166" t="n">
         <v>78</v>
       </c>
       <c r="U166" t="n">
-        <v>26.8</v>
+        <v>12</v>
       </c>
       <c r="V166" t="n">
         <v>50</v>
@@ -53143,38 +53123,42 @@
       <c r="W166" t="inlineStr"/>
       <c r="X166" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y166" t="inlineStr">
+      <c r="AB166" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA166" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AD166" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AD166" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AE166" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF166" t="inlineStr"/>
@@ -53186,32 +53170,32 @@
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AL166" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>Last 5 games: 3/17, 1 HR</t>
+          <t>Last 7 games: 2/10, 0 HR</t>
         </is>
       </c>
       <c r="AN166" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.1% barrel, 13.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 13.7 HR allowed</t>
         </is>
       </c>
       <c r="AO166" t="inlineStr">
@@ -53221,102 +53205,102 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AQ166" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="AR166" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>86.13</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr">
         <is>
-          <t>96.3696</t>
+          <t>97.085</t>
         </is>
       </c>
       <c r="AT166" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.3416</t>
         </is>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.0809</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>0.3116</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>69.32</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>35.69</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>0.1392</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="BD166" t="inlineStr">
         <is>
-          <t>32.83</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BE166" t="inlineStr">
         <is>
-          <t>87.45</t>
+          <t>90.03</t>
         </is>
       </c>
       <c r="BF166" t="inlineStr">
         <is>
-          <t>0.3172</t>
+          <t>0.3686</t>
         </is>
       </c>
       <c r="BG166" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t>0.146</t>
         </is>
       </c>
       <c r="BH166" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI166" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>230 deg</t>
         </is>
       </c>
       <c r="BJ166" t="inlineStr">
@@ -53326,27 +53310,27 @@
       </c>
       <c r="BK166" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
         </is>
       </c>
       <c r="BL166" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>58</t>
         </is>
       </c>
       <c r="BM166" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN166" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BO166" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BP166" t="inlineStr"/>
@@ -53367,22 +53351,22 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>645302</t>
+          <t>701785</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Victor Robles</t>
+          <t>Kaelen Culpepper</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -53397,26 +53381,26 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Hayden Wesneski</t>
+          <t>Jesús Luzardo</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>669713</t>
+          <t>666200</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>35.6</v>
+        <v>36</v>
       </c>
       <c r="M167" t="inlineStr">
         <is>
@@ -53430,26 +53414,26 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P167" t="n">
-        <v>3.4</v>
+        <v>19.6</v>
       </c>
       <c r="Q167" t="n">
-        <v>46.9</v>
+        <v>20.8</v>
       </c>
       <c r="R167" t="n">
-        <v>56.6</v>
+        <v>62.6</v>
       </c>
       <c r="S167" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T167" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U167" t="n">
-        <v>39.7</v>
+        <v>26.8</v>
       </c>
       <c r="V167" t="n">
         <v>50</v>
@@ -53467,7 +53451,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -53488,7 +53472,7 @@
       <c r="AD167" t="inlineStr"/>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr"/>
@@ -53500,32 +53484,32 @@
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL167" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>Contact streak: 5/13 over last 7 games</t>
+          <t>Last 5 games: 3/17, 1 HR</t>
         </is>
       </c>
       <c r="AN167" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.4% barrel, 3.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.1% barrel, 13.2 HR allowed</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
@@ -53535,102 +53519,102 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AQ167" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AR167" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr">
         <is>
-          <t>94.474</t>
+          <t>96.3696</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr">
         <is>
-          <t>0.3095</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>0.0855</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>0.251</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>67.77</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>27.43</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>0.0549</t>
+          <t>0.177</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="BD167" t="inlineStr">
         <is>
-          <t>40.14</t>
+          <t>32.83</t>
         </is>
       </c>
       <c r="BE167" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>87.45</t>
         </is>
       </c>
       <c r="BF167" t="inlineStr">
         <is>
-          <t>0.4563</t>
+          <t>0.3172</t>
         </is>
       </c>
       <c r="BG167" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="BH167" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="BI167" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ167" t="inlineStr">
@@ -53640,27 +53624,27 @@
       </c>
       <c r="BK167" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=29.7573&amp;lon=-95.3555</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
         </is>
       </c>
       <c r="BL167" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BM167" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="BN167" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BO167" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BP167" t="inlineStr"/>
@@ -53681,27 +53665,27 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>702332</t>
+          <t>645302</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Caleb Durbin</t>
+          <t>Victor Robles</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-08-15T23:15:00Z</t>
+          <t>2026-08-15T23:10:00Z</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -53711,17 +53695,17 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Jared Jones</t>
+          <t>Hayden Wesneski</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>683003</t>
+          <t>669713</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -53730,7 +53714,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>34.4</v>
+        <v>35.6</v>
       </c>
       <c r="M168" t="inlineStr">
         <is>
@@ -53748,22 +53732,22 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="Q168" t="n">
-        <v>40</v>
+        <v>46.9</v>
       </c>
       <c r="R168" t="n">
-        <v>32.3</v>
+        <v>56.6</v>
       </c>
       <c r="S168" t="n">
-        <v>76.2</v>
+        <v>52.4</v>
       </c>
       <c r="T168" t="n">
         <v>50</v>
       </c>
       <c r="U168" t="n">
-        <v>37.8</v>
+        <v>39.7</v>
       </c>
       <c r="V168" t="n">
         <v>50</v>
@@ -53781,7 +53765,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -53802,7 +53786,7 @@
       <c r="AD168" t="inlineStr"/>
       <c r="AE168" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF168" t="inlineStr"/>
@@ -53819,162 +53803,162 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AL168" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM168" t="inlineStr">
+        <is>
+          <t>Contact streak: 5/13 over last 7 games</t>
+        </is>
+      </c>
+      <c r="AN168" t="inlineStr">
+        <is>
+          <t>same-side matchup; pitcher baseline 9.4% barrel, 3.5 HR allowed</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>20.12</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>84.21</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>94.474</t>
+        </is>
+      </c>
+      <c r="AT168" t="inlineStr">
+        <is>
+          <t>0.3095</t>
+        </is>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>0.0855</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t>0.258</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>67.77</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>27.43</t>
+        </is>
+      </c>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>0.0549</t>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr">
+        <is>
+          <t>9.38</t>
+        </is>
+      </c>
+      <c r="BD168" t="inlineStr">
+        <is>
+          <t>40.14</t>
+        </is>
+      </c>
+      <c r="BE168" t="inlineStr">
+        <is>
+          <t>89.49</t>
+        </is>
+      </c>
+      <c r="BF168" t="inlineStr">
+        <is>
+          <t>0.4563</t>
+        </is>
+      </c>
+      <c r="BG168" t="inlineStr">
+        <is>
+          <t>0.1823</t>
+        </is>
+      </c>
+      <c r="BH168" t="inlineStr">
+        <is>
+          <t>26.98</t>
+        </is>
+      </c>
+      <c r="BI168" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BJ168" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK168" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=29.7573&amp;lon=-95.3555</t>
+        </is>
+      </c>
+      <c r="BL168" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="BM168" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM168" t="inlineStr">
-        <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
-        </is>
-      </c>
-      <c r="AN168" t="inlineStr">
-        <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 10.0 HR allowed</t>
-        </is>
-      </c>
-      <c r="AO168" t="inlineStr">
-        <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AP168" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="AQ168" t="inlineStr">
-        <is>
-          <t>26.69</t>
-        </is>
-      </c>
-      <c r="AR168" t="inlineStr">
-        <is>
-          <t>84.22</t>
-        </is>
-      </c>
-      <c r="AS168" t="inlineStr">
-        <is>
-          <t>95.8483</t>
-        </is>
-      </c>
-      <c r="AT168" t="inlineStr">
-        <is>
-          <t>0.3354</t>
-        </is>
-      </c>
-      <c r="AU168" t="inlineStr">
-        <is>
-          <t>0.0937</t>
-        </is>
-      </c>
-      <c r="AV168" t="inlineStr">
-        <is>
-          <t>0.2952</t>
-        </is>
-      </c>
-      <c r="AW168" t="inlineStr">
-        <is>
-          <t>68.88</t>
-        </is>
-      </c>
-      <c r="AX168" t="inlineStr">
-        <is>
-          <t>5.44</t>
-        </is>
-      </c>
-      <c r="AY168" t="inlineStr">
-        <is>
-          <t>41.72</t>
-        </is>
-      </c>
-      <c r="AZ168" t="inlineStr">
-        <is>
-          <t>19.26</t>
-        </is>
-      </c>
-      <c r="BA168" t="inlineStr">
-        <is>
-          <t>11.7</t>
-        </is>
-      </c>
-      <c r="BB168" t="inlineStr">
-        <is>
-          <t>0.1485</t>
-        </is>
-      </c>
-      <c r="BC168" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="BD168" t="inlineStr">
-        <is>
-          <t>39.3</t>
-        </is>
-      </c>
-      <c r="BE168" t="inlineStr">
-        <is>
-          <t>89.5</t>
-        </is>
-      </c>
-      <c r="BF168" t="inlineStr">
-        <is>
-          <t>0.387</t>
-        </is>
-      </c>
-      <c r="BG168" t="inlineStr">
-        <is>
-          <t>0.167</t>
-        </is>
-      </c>
-      <c r="BH168" t="inlineStr">
-        <is>
-          <t>26.4</t>
-        </is>
-      </c>
-      <c r="BI168" t="inlineStr">
-        <is>
-          <t>In From RF</t>
-        </is>
-      </c>
-      <c r="BJ168" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BK168" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=40.4469&amp;lon=-80.0057</t>
-        </is>
-      </c>
-      <c r="BL168" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="BM168" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BN168" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BO168" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BP168" t="inlineStr"/>
@@ -53995,56 +53979,56 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>664728</t>
+          <t>702332</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Kyle Isbel</t>
+          <t>Caleb Durbin</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-08-16T01:38:00Z</t>
+          <t>2026-08-15T23:15:00Z</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Reid Detmers</t>
+          <t>Jared Jones</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>672282</t>
+          <t>683003</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>34.2</v>
+        <v>34.4</v>
       </c>
       <c r="M169" t="inlineStr">
         <is>
@@ -54058,26 +54042,26 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P169" t="n">
-        <v>13</v>
+        <v>5.1</v>
       </c>
       <c r="Q169" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R169" t="n">
-        <v>54.7</v>
+        <v>32.3</v>
       </c>
       <c r="S169" t="n">
-        <v>40.2</v>
+        <v>76.2</v>
       </c>
       <c r="T169" t="n">
         <v>50</v>
       </c>
       <c r="U169" t="n">
-        <v>18.3</v>
+        <v>37.8</v>
       </c>
       <c r="V169" t="n">
         <v>50</v>
@@ -54085,42 +54069,38 @@
       <c r="W169" t="inlineStr"/>
       <c r="X169" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y169" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z169" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA169" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB169" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD169" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD169" t="inlineStr"/>
       <c r="AE169" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF169" t="inlineStr"/>
@@ -54137,12 +54117,12 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL169" t="inlineStr">
@@ -54152,12 +54132,12 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/22, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AN169" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 13.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
@@ -54167,102 +54147,102 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AQ169" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>26.69</t>
         </is>
       </c>
       <c r="AR169" t="inlineStr">
         <is>
-          <t>88.43</t>
+          <t>84.22</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr">
         <is>
-          <t>99.1098</t>
+          <t>95.8483</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr">
         <is>
-          <t>0.3019</t>
+          <t>0.3354</t>
         </is>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>0.0763</t>
+          <t>0.0937</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>0.2587</t>
+          <t>0.2952</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>71.24</t>
+          <t>68.88</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>14.88</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>33.09</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>19.26</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>0.1064</t>
+          <t>0.1485</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BD169" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="BE169" t="inlineStr">
         <is>
-          <t>90.03</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="BF169" t="inlineStr">
         <is>
-          <t>0.3686</t>
+          <t>0.387</t>
         </is>
       </c>
       <c r="BG169" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="BH169" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="BI169" t="inlineStr">
         <is>
-          <t>230 deg</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BJ169" t="inlineStr">
@@ -54272,12 +54252,12 @@
       </c>
       <c r="BK169" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=40.4469&amp;lon=-80.0057</t>
         </is>
       </c>
       <c r="BL169" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>87</t>
         </is>
       </c>
       <c r="BM169" t="inlineStr">
@@ -54287,12 +54267,12 @@
       </c>
       <c r="BN169" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BO169" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BP169" t="inlineStr"/>
@@ -54313,47 +54293,47 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>664728</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Kyle Isbel</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-08-15T23:10:00Z</t>
+          <t>2026-08-16T01:38:00Z</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Wandy Peralta</t>
+          <t>Reid Detmers</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>593974</t>
+          <t>672282</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -54362,7 +54342,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="M170" t="inlineStr">
         <is>
@@ -54376,26 +54356,26 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P170" t="n">
-        <v>2.4</v>
+        <v>13</v>
       </c>
       <c r="Q170" t="n">
-        <v>18.1</v>
+        <v>41</v>
       </c>
       <c r="R170" t="n">
-        <v>50.1</v>
+        <v>54.7</v>
       </c>
       <c r="S170" t="n">
-        <v>93.2</v>
+        <v>40.2</v>
       </c>
       <c r="T170" t="n">
         <v>50</v>
       </c>
       <c r="U170" t="n">
-        <v>52.1</v>
+        <v>18.3</v>
       </c>
       <c r="V170" t="n">
         <v>50</v>
@@ -54403,35 +54383,39 @@
       <c r="W170" t="inlineStr"/>
       <c r="X170" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y170" t="inlineStr">
+      <c r="AB170" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA170" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AD170" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AE170" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -54451,12 +54435,12 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL170" t="inlineStr">
@@ -54466,12 +54450,12 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>Contact streak: 10/29 over last 7 games</t>
+          <t>Last 7 games: 2/22, 1 HR</t>
         </is>
       </c>
       <c r="AN170" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.6% barrel, 5.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 13.7 HR allowed</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
@@ -54481,102 +54465,102 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AQ170" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>35.4</t>
         </is>
       </c>
       <c r="AR170" t="inlineStr">
         <is>
-          <t>84.38</t>
+          <t>88.43</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr">
         <is>
-          <t>92.4903</t>
+          <t>99.1098</t>
         </is>
       </c>
       <c r="AT170" t="inlineStr">
         <is>
-          <t>0.3457</t>
+          <t>0.3019</t>
         </is>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>0.0713</t>
+          <t>0.0763</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>0.3212</t>
+          <t>0.2587</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>62.8</t>
+          <t>71.24</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>14.88</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>33.09</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>23.16</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>0.0733</t>
+          <t>0.1064</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="BD170" t="inlineStr">
         <is>
-          <t>33.96</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BE170" t="inlineStr">
         <is>
-          <t>87.04</t>
+          <t>90.03</t>
         </is>
       </c>
       <c r="BF170" t="inlineStr">
         <is>
-          <t>0.3759</t>
+          <t>0.3686</t>
         </is>
       </c>
       <c r="BG170" t="inlineStr">
         <is>
-          <t>0.1169</t>
+          <t>0.146</t>
         </is>
       </c>
       <c r="BH170" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI170" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>230 deg</t>
         </is>
       </c>
       <c r="BJ170" t="inlineStr">
@@ -54586,12 +54570,12 @@
       </c>
       <c r="BK170" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=41.4962&amp;lon=-81.6852</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
         </is>
       </c>
       <c r="BL170" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>58</t>
         </is>
       </c>
       <c r="BM170" t="inlineStr">
@@ -54601,12 +54585,12 @@
       </c>
       <c r="BN170" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BO170" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BP170" t="inlineStr"/>
@@ -54627,27 +54611,27 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>663968</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Jake Mangum</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-08-15T23:15:00Z</t>
+          <t>2026-08-15T23:10:00Z</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -54657,26 +54641,26 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Sonny Gray</t>
+          <t>Wandy Peralta</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>543243</t>
+          <t>593974</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L171" t="n">
-        <v>34</v>
+        <v>34.1</v>
       </c>
       <c r="M171" t="inlineStr">
         <is>
@@ -54690,26 +54674,26 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P171" t="n">
-        <v>6.4</v>
+        <v>2.4</v>
       </c>
       <c r="Q171" t="n">
-        <v>34.2</v>
+        <v>18.1</v>
       </c>
       <c r="R171" t="n">
-        <v>32.3</v>
+        <v>50.1</v>
       </c>
       <c r="S171" t="n">
-        <v>64.3</v>
+        <v>93.2</v>
       </c>
       <c r="T171" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U171" t="n">
-        <v>43.2</v>
+        <v>52.1</v>
       </c>
       <c r="V171" t="n">
         <v>50</v>
@@ -54727,7 +54711,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -54765,12 +54749,12 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL171" t="inlineStr">
@@ -54780,12 +54764,12 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/28, 1 HR</t>
+          <t>Contact streak: 10/29 over last 7 games</t>
         </is>
       </c>
       <c r="AN171" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.4% barrel, 16.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.6% barrel, 5.0 HR allowed</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">
@@ -54795,102 +54779,102 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AQ171" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="AR171" t="inlineStr">
         <is>
-          <t>85.97</t>
+          <t>84.38</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr">
         <is>
-          <t>96.7417</t>
+          <t>92.4903</t>
         </is>
       </c>
       <c r="AT171" t="inlineStr">
         <is>
-          <t>0.3339</t>
+          <t>0.3457</t>
         </is>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>0.0822</t>
+          <t>0.0713</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>0.2837</t>
+          <t>0.3212</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>67.58</t>
+          <t>62.8</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>23.16</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>0.0867</t>
+          <t>0.0733</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="BD171" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>33.96</t>
         </is>
       </c>
       <c r="BE171" t="inlineStr">
         <is>
-          <t>89.11</t>
+          <t>87.04</t>
         </is>
       </c>
       <c r="BF171" t="inlineStr">
         <is>
-          <t>0.3824</t>
+          <t>0.3759</t>
         </is>
       </c>
       <c r="BG171" t="inlineStr">
         <is>
-          <t>0.1362</t>
+          <t>0.1169</t>
         </is>
       </c>
       <c r="BH171" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>16.92</t>
         </is>
       </c>
       <c r="BI171" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ171" t="inlineStr">
@@ -54900,12 +54884,12 @@
       </c>
       <c r="BK171" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=40.4469&amp;lon=-80.0057</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=41.4962&amp;lon=-81.6852</t>
         </is>
       </c>
       <c r="BL171" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BM171" t="inlineStr">
@@ -54915,12 +54899,12 @@
       </c>
       <c r="BN171" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BO171" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BP171" t="inlineStr"/>
@@ -54941,27 +54925,27 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>670764</t>
+          <t>663968</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>Jake Mangum</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-08-15T22:10:00Z</t>
+          <t>2026-08-15T23:15:00Z</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -54971,17 +54955,17 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Sonny Gray</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>680694</t>
+          <t>543243</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -54990,7 +54974,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>33.8</v>
+        <v>34</v>
       </c>
       <c r="M172" t="inlineStr">
         <is>
@@ -55008,22 +54992,22 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="Q172" t="n">
-        <v>33</v>
+        <v>34.2</v>
       </c>
       <c r="R172" t="n">
-        <v>48.1</v>
+        <v>32.3</v>
       </c>
       <c r="S172" t="n">
-        <v>44.8</v>
+        <v>64.3</v>
       </c>
       <c r="T172" t="n">
         <v>75</v>
       </c>
       <c r="U172" t="n">
-        <v>59.6</v>
+        <v>43.2</v>
       </c>
       <c r="V172" t="n">
         <v>50</v>
@@ -55041,7 +55025,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -55079,27 +55063,27 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AL172" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 8/28, 1 HR</t>
         </is>
       </c>
       <c r="AN172" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.2% barrel, 10.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.4% barrel, 16.6 HR allowed</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
@@ -55109,102 +55093,102 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AQ172" t="inlineStr">
         <is>
-          <t>22.69</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="AR172" t="inlineStr">
         <is>
-          <t>85.88</t>
+          <t>85.97</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr">
         <is>
-          <t>95.367</t>
+          <t>96.7417</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr">
         <is>
-          <t>0.2691</t>
+          <t>0.3339</t>
         </is>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>0.0759</t>
+          <t>0.0822</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>0.2512</t>
+          <t>0.2837</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>68.35</t>
+          <t>67.58</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>37.56</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>29.68</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>0.0871</t>
+          <t>0.0867</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BD172" t="inlineStr">
         <is>
-          <t>37.71</t>
+          <t>38.53</t>
         </is>
       </c>
       <c r="BE172" t="inlineStr">
         <is>
-          <t>88.47</t>
+          <t>89.11</t>
         </is>
       </c>
       <c r="BF172" t="inlineStr">
         <is>
-          <t>0.3634</t>
+          <t>0.3824</t>
         </is>
       </c>
       <c r="BG172" t="inlineStr">
         <is>
-          <t>0.1366</t>
+          <t>0.1362</t>
         </is>
       </c>
       <c r="BH172" t="inlineStr">
         <is>
-          <t>22.94</t>
+          <t>22.99</t>
         </is>
       </c>
       <c r="BI172" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BJ172" t="inlineStr">
@@ -55214,27 +55198,27 @@
       </c>
       <c r="BK172" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=27.7682&amp;lon=-82.6534</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=40.4469&amp;lon=-80.0057</t>
         </is>
       </c>
       <c r="BL172" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>87</t>
         </is>
       </c>
       <c r="BM172" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN172" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BO172" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BP172" t="inlineStr"/>
@@ -55255,27 +55239,27 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-08-15T23:10:00Z</t>
+          <t>2026-08-15T22:10:00Z</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -55285,26 +55269,26 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Wandy Peralta</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>593974</t>
+          <t>680694</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L173" t="n">
-        <v>33.2</v>
+        <v>33.8</v>
       </c>
       <c r="M173" t="inlineStr">
         <is>
@@ -55318,26 +55302,26 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P173" t="n">
-        <v>20.9</v>
+        <v>5.6</v>
       </c>
       <c r="Q173" t="n">
-        <v>18.1</v>
+        <v>33</v>
       </c>
       <c r="R173" t="n">
-        <v>50.1</v>
+        <v>48.1</v>
       </c>
       <c r="S173" t="n">
-        <v>64.3</v>
+        <v>44.8</v>
       </c>
       <c r="T173" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U173" t="n">
-        <v>0.8</v>
+        <v>59.6</v>
       </c>
       <c r="V173" t="n">
         <v>50</v>
@@ -55355,7 +55339,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -55376,7 +55360,7 @@
       <c r="AD173" t="inlineStr"/>
       <c r="AE173" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF173" t="inlineStr"/>
@@ -55393,27 +55377,27 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL173" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.6% barrel, 5.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.2% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
@@ -55423,102 +55407,102 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="AQ173" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>22.69</t>
         </is>
       </c>
       <c r="AR173" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>85.88</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr">
         <is>
-          <t>98.5438</t>
+          <t>95.367</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.2691</t>
         </is>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0759</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2512</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>68.35</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>37.56</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>29.68</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.0871</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="BD173" t="inlineStr">
         <is>
-          <t>33.96</t>
+          <t>37.71</t>
         </is>
       </c>
       <c r="BE173" t="inlineStr">
         <is>
-          <t>87.04</t>
+          <t>88.47</t>
         </is>
       </c>
       <c r="BF173" t="inlineStr">
         <is>
-          <t>0.3759</t>
+          <t>0.3634</t>
         </is>
       </c>
       <c r="BG173" t="inlineStr">
         <is>
-          <t>0.1169</t>
+          <t>0.1366</t>
         </is>
       </c>
       <c r="BH173" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>22.94</t>
         </is>
       </c>
       <c r="BI173" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ173" t="inlineStr">
@@ -55528,27 +55512,27 @@
       </c>
       <c r="BK173" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=41.4962&amp;lon=-81.6852</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=27.7682&amp;lon=-82.6534</t>
         </is>
       </c>
       <c r="BL173" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BM173" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
       <c r="BN173" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BO173" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BP173" t="inlineStr"/>
@@ -55569,27 +55553,27 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>669707</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Jared Triolo</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-08-15T23:15:00Z</t>
+          <t>2026-08-15T23:10:00Z</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -55599,22 +55583,22 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Sonny Gray</t>
+          <t>Wandy Peralta</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>543243</t>
+          <t>593974</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L174" t="n">
@@ -55636,22 +55620,22 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>17</v>
+        <v>20.9</v>
       </c>
       <c r="Q174" t="n">
-        <v>35.9</v>
+        <v>18.1</v>
       </c>
       <c r="R174" t="n">
-        <v>32.3</v>
+        <v>50.1</v>
       </c>
       <c r="S174" t="n">
-        <v>44.8</v>
+        <v>64.3</v>
       </c>
       <c r="T174" t="n">
         <v>50</v>
       </c>
       <c r="U174" t="n">
-        <v>47.2</v>
+        <v>0.8</v>
       </c>
       <c r="V174" t="n">
         <v>50</v>
@@ -55669,7 +55653,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -55690,7 +55674,7 @@
       <c r="AD174" t="inlineStr"/>
       <c r="AE174" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF174" t="inlineStr"/>
@@ -55707,27 +55691,27 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL174" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/16, 1 HR</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.6% barrel, 5.0 HR allowed</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
@@ -55737,102 +55721,102 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AQ174" t="inlineStr">
         <is>
-          <t>37.43</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="AR174" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr">
         <is>
-          <t>98.6923</t>
+          <t>98.5438</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>0.0978</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>0.2981</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>21.03</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>0.0905</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="BD174" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>33.96</t>
         </is>
       </c>
       <c r="BE174" t="inlineStr">
         <is>
-          <t>89.11</t>
+          <t>87.04</t>
         </is>
       </c>
       <c r="BF174" t="inlineStr">
         <is>
-          <t>0.3824</t>
+          <t>0.3759</t>
         </is>
       </c>
       <c r="BG174" t="inlineStr">
         <is>
-          <t>0.1362</t>
+          <t>0.1169</t>
         </is>
       </c>
       <c r="BH174" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>16.92</t>
         </is>
       </c>
       <c r="BI174" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BJ174" t="inlineStr">
@@ -55842,12 +55826,12 @@
       </c>
       <c r="BK174" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=40.4469&amp;lon=-80.0057</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=41.4962&amp;lon=-81.6852</t>
         </is>
       </c>
       <c r="BL174" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BM174" t="inlineStr">
@@ -55857,12 +55841,12 @@
       </c>
       <c r="BN174" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BO174" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BP174" t="inlineStr"/>
@@ -55883,27 +55867,27 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>543877</t>
+          <t>669707</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Christian Vázquez</t>
+          <t>Jared Triolo</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-08-15T23:10:00Z</t>
+          <t>2026-08-15T23:15:00Z</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -55918,12 +55902,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Emerson Hancock</t>
+          <t>Sonny Gray</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>676106</t>
+          <t>543243</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -55932,7 +55916,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="M175" t="inlineStr">
         <is>
@@ -55950,13 +55934,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>3.4</v>
+        <v>17</v>
       </c>
       <c r="Q175" t="n">
-        <v>46.2</v>
+        <v>35.9</v>
       </c>
       <c r="R175" t="n">
-        <v>56.6</v>
+        <v>32.3</v>
       </c>
       <c r="S175" t="n">
         <v>44.8</v>
@@ -55965,7 +55949,7 @@
         <v>50</v>
       </c>
       <c r="U175" t="n">
-        <v>13.6</v>
+        <v>47.2</v>
       </c>
       <c r="V175" t="n">
         <v>50</v>
@@ -56021,162 +56005,162 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL175" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM175" t="inlineStr">
+        <is>
+          <t>Last 7 games: 5/16, 1 HR</t>
+        </is>
+      </c>
+      <c r="AN175" t="inlineStr">
+        <is>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.6 HR allowed</t>
+        </is>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AP175" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t>37.43</t>
+        </is>
+      </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>88.09</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>98.6923</t>
+        </is>
+      </c>
+      <c r="AT175" t="inlineStr">
+        <is>
+          <t>0.341</t>
+        </is>
+      </c>
+      <c r="AU175" t="inlineStr">
+        <is>
+          <t>0.0978</t>
+        </is>
+      </c>
+      <c r="AV175" t="inlineStr">
+        <is>
+          <t>0.2981</t>
+        </is>
+      </c>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>70.9</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>7.79</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr">
+        <is>
+          <t>37.99</t>
+        </is>
+      </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>21.03</t>
+        </is>
+      </c>
+      <c r="BA175" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="BB175" t="inlineStr">
+        <is>
+          <t>0.0905</t>
+        </is>
+      </c>
+      <c r="BC175" t="inlineStr">
+        <is>
+          <t>7.42</t>
+        </is>
+      </c>
+      <c r="BD175" t="inlineStr">
+        <is>
+          <t>38.53</t>
+        </is>
+      </c>
+      <c r="BE175" t="inlineStr">
+        <is>
+          <t>89.11</t>
+        </is>
+      </c>
+      <c r="BF175" t="inlineStr">
+        <is>
+          <t>0.3824</t>
+        </is>
+      </c>
+      <c r="BG175" t="inlineStr">
+        <is>
+          <t>0.1362</t>
+        </is>
+      </c>
+      <c r="BH175" t="inlineStr">
+        <is>
+          <t>22.99</t>
+        </is>
+      </c>
+      <c r="BI175" t="inlineStr">
+        <is>
+          <t>In From RF</t>
+        </is>
+      </c>
+      <c r="BJ175" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK175" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=40.4469&amp;lon=-80.0057</t>
+        </is>
+      </c>
+      <c r="BL175" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="BM175" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AM175" t="inlineStr">
-        <is>
-          <t>Last 7 games: 4/19, 0 HR</t>
-        </is>
-      </c>
-      <c r="AN175" t="inlineStr">
-        <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 15.0 HR allowed</t>
-        </is>
-      </c>
-      <c r="AO175" t="inlineStr">
-        <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AP175" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="AQ175" t="inlineStr">
-        <is>
-          <t>24.25</t>
-        </is>
-      </c>
-      <c r="AR175" t="inlineStr">
-        <is>
-          <t>85.83</t>
-        </is>
-      </c>
-      <c r="AS175" t="inlineStr">
-        <is>
-          <t>95.4798</t>
-        </is>
-      </c>
-      <c r="AT175" t="inlineStr">
-        <is>
-          <t>0.2762</t>
-        </is>
-      </c>
-      <c r="AU175" t="inlineStr">
-        <is>
-          <t>0.076</t>
-        </is>
-      </c>
-      <c r="AV175" t="inlineStr">
-        <is>
-          <t>0.2451</t>
-        </is>
-      </c>
-      <c r="AW175" t="inlineStr">
-        <is>
-          <t>66.02</t>
-        </is>
-      </c>
-      <c r="AX175" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="AY175" t="inlineStr">
-        <is>
-          <t>33.72</t>
-        </is>
-      </c>
-      <c r="AZ175" t="inlineStr">
-        <is>
-          <t>25.75</t>
-        </is>
-      </c>
-      <c r="BA175" t="inlineStr">
-        <is>
-          <t>4.4</t>
-        </is>
-      </c>
-      <c r="BB175" t="inlineStr">
-        <is>
-          <t>0.0997</t>
-        </is>
-      </c>
-      <c r="BC175" t="inlineStr">
-        <is>
-          <t>8.26</t>
-        </is>
-      </c>
-      <c r="BD175" t="inlineStr">
-        <is>
-          <t>42.08</t>
-        </is>
-      </c>
-      <c r="BE175" t="inlineStr">
-        <is>
-          <t>89.35</t>
-        </is>
-      </c>
-      <c r="BF175" t="inlineStr">
-        <is>
-          <t>0.4316</t>
-        </is>
-      </c>
-      <c r="BG175" t="inlineStr">
-        <is>
-          <t>0.1717</t>
-        </is>
-      </c>
-      <c r="BH175" t="inlineStr">
-        <is>
-          <t>28.52</t>
-        </is>
-      </c>
-      <c r="BI175" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BJ175" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BK175" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=29.7573&amp;lon=-95.3555</t>
-        </is>
-      </c>
-      <c r="BL175" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="BM175" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="BN175" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BO175" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BP175" t="inlineStr"/>
@@ -56197,32 +56181,32 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>623168</t>
+          <t>543877</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Tyler Heineman</t>
+          <t>Christian Vázquez</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-08-16T01:38:00Z</t>
+          <t>2026-08-15T23:10:00Z</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -56232,12 +56216,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Randy Dobnak</t>
+          <t>Emerson Hancock</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>677976</t>
+          <t>676106</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -56246,7 +56230,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>31.4</v>
+        <v>33.1</v>
       </c>
       <c r="M176" t="inlineStr">
         <is>
@@ -56260,26 +56244,26 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P176" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q176" t="n">
-        <v>34.4</v>
+        <v>46.2</v>
       </c>
       <c r="R176" t="n">
-        <v>54.7</v>
+        <v>56.6</v>
       </c>
       <c r="S176" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T176" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U176" t="n">
-        <v>32</v>
+        <v>13.6</v>
       </c>
       <c r="V176" t="n">
         <v>50</v>
@@ -56287,39 +56271,35 @@
       <c r="W176" t="inlineStr"/>
       <c r="X176" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y176" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA176" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD176" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD176" t="inlineStr"/>
       <c r="AE176" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -56344,7 +56324,7 @@
       </c>
       <c r="AK176" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL176" t="inlineStr">
@@ -56354,12 +56334,12 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>Contact streak: 4/12 over last 7 games</t>
+          <t>Last 7 games: 4/19, 0 HR</t>
         </is>
       </c>
       <c r="AN176" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 4.8% barrel, 1.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
@@ -56369,102 +56349,102 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AQ176" t="inlineStr">
         <is>
-          <t>15.47</t>
+          <t>24.25</t>
         </is>
       </c>
       <c r="AR176" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>85.83</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr">
         <is>
-          <t>92.7282</t>
+          <t>95.4798</t>
         </is>
       </c>
       <c r="AT176" t="inlineStr">
         <is>
-          <t>0.2832</t>
+          <t>0.2762</t>
         </is>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>0.0573</t>
+          <t>0.076</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>0.2604</t>
+          <t>0.2451</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>65.68</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>33.72</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>0.0766</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="BD176" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BE176" t="inlineStr">
         <is>
-          <t>91.74</t>
+          <t>89.35</t>
         </is>
       </c>
       <c r="BF176" t="inlineStr">
         <is>
-          <t>0.4227</t>
+          <t>0.4316</t>
         </is>
       </c>
       <c r="BG176" t="inlineStr">
         <is>
-          <t>0.1289</t>
+          <t>0.1717</t>
         </is>
       </c>
       <c r="BH176" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>28.52</t>
         </is>
       </c>
       <c r="BI176" t="inlineStr">
         <is>
-          <t>230 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ176" t="inlineStr">
@@ -56474,27 +56454,27 @@
       </c>
       <c r="BK176" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=29.7573&amp;lon=-95.3555</t>
         </is>
       </c>
       <c r="BL176" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>69</t>
         </is>
       </c>
       <c r="BM176" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BN176" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BO176" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BP176" t="inlineStr"/>
@@ -56515,32 +56495,32 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>686765</t>
+          <t>623168</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Nick Sogard</t>
+          <t>Tyler Heineman</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-08-15T23:15:00Z</t>
+          <t>2026-08-16T01:38:00Z</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -56550,12 +56530,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Jared Jones</t>
+          <t>Randy Dobnak</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>683003</t>
+          <t>677976</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -56564,7 +56544,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>31.1</v>
+        <v>31.4</v>
       </c>
       <c r="M177" t="inlineStr">
         <is>
@@ -56578,26 +56558,26 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P177" t="n">
-        <v>4.8</v>
+        <v>0.3</v>
       </c>
       <c r="Q177" t="n">
-        <v>38.9</v>
+        <v>34.4</v>
       </c>
       <c r="R177" t="n">
-        <v>32.3</v>
+        <v>54.7</v>
       </c>
       <c r="S177" t="n">
-        <v>44.8</v>
+        <v>40.2</v>
       </c>
       <c r="T177" t="n">
         <v>75</v>
       </c>
       <c r="U177" t="n">
-        <v>26.4</v>
+        <v>32</v>
       </c>
       <c r="V177" t="n">
         <v>50</v>
@@ -56605,38 +56585,42 @@
       <c r="W177" t="inlineStr"/>
       <c r="X177" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y177" t="inlineStr">
+      <c r="AB177" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA177" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AD177" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AD177" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AE177" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr"/>
@@ -56653,12 +56637,12 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AL177" t="inlineStr">
@@ -56668,12 +56652,12 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 0 HR</t>
+          <t>Contact streak: 4/12 over last 7 games</t>
         </is>
       </c>
       <c r="AN177" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.0% barrel, 10.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 4.8% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
@@ -56683,102 +56667,102 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AQ177" t="inlineStr">
         <is>
-          <t>26.37</t>
+          <t>15.47</t>
         </is>
       </c>
       <c r="AR177" t="inlineStr">
         <is>
-          <t>84.95</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr">
         <is>
-          <t>95.108</t>
+          <t>92.7282</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr">
         <is>
-          <t>0.3337</t>
+          <t>0.2832</t>
         </is>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>0.0778</t>
+          <t>0.0573</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>0.3118</t>
+          <t>0.2604</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>68.92</t>
+          <t>65.68</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>44.33</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>22.06</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>0.0777</t>
+          <t>0.0766</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="BD177" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>46.08</t>
         </is>
       </c>
       <c r="BE177" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>91.74</t>
         </is>
       </c>
       <c r="BF177" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>0.4227</t>
         </is>
       </c>
       <c r="BG177" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.1289</t>
         </is>
       </c>
       <c r="BH177" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="BI177" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>230 deg</t>
         </is>
       </c>
       <c r="BJ177" t="inlineStr">
@@ -56788,12 +56772,12 @@
       </c>
       <c r="BK177" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=40.4469&amp;lon=-80.0057</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8003&amp;lon=-117.8827</t>
         </is>
       </c>
       <c r="BL177" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>58</t>
         </is>
       </c>
       <c r="BM177" t="inlineStr">
@@ -56803,12 +56787,12 @@
       </c>
       <c r="BN177" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BO177" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BP177" t="inlineStr"/>
@@ -56829,32 +56813,32 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>670032</t>
+          <t>686765</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Nicky Lopez</t>
+          <t>Nick Sogard</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-08-16T01:40:00Z</t>
+          <t>2026-08-15T23:15:00Z</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -56864,12 +56848,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>J.T. Ginn</t>
+          <t>Jared Jones</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>669372</t>
+          <t>683003</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -56878,7 +56862,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>30.1</v>
+        <v>31.1</v>
       </c>
       <c r="M178" t="inlineStr">
         <is>
@@ -56892,26 +56876,26 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P178" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="Q178" t="n">
-        <v>30.2</v>
+        <v>38.9</v>
       </c>
       <c r="R178" t="n">
-        <v>56.4</v>
+        <v>32.3</v>
       </c>
       <c r="S178" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T178" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U178" t="n">
-        <v>2</v>
+        <v>26.4</v>
       </c>
       <c r="V178" t="n">
         <v>50</v>
@@ -56919,42 +56903,38 @@
       <c r="W178" t="inlineStr"/>
       <c r="X178" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y178" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z178" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA178" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB178" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD178" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD178" t="inlineStr"/>
       <c r="AE178" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF178" t="inlineStr"/>
@@ -56971,12 +56951,12 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL178" t="inlineStr">
@@ -56986,12 +56966,12 @@
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/15, 0 HR</t>
+          <t>Last 7 games: 8/27, 0 HR</t>
         </is>
       </c>
       <c r="AN178" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 14.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.0% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
@@ -57001,102 +56981,102 @@
       </c>
       <c r="AP178" t="inlineStr">
         <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="AQ178" t="inlineStr">
+        <is>
+          <t>26.37</t>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>84.95</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr">
+        <is>
+          <t>95.108</t>
+        </is>
+      </c>
+      <c r="AT178" t="inlineStr">
+        <is>
+          <t>0.3337</t>
+        </is>
+      </c>
+      <c r="AU178" t="inlineStr">
+        <is>
+          <t>0.0778</t>
+        </is>
+      </c>
+      <c r="AV178" t="inlineStr">
+        <is>
+          <t>0.3118</t>
+        </is>
+      </c>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>68.92</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr">
+        <is>
+          <t>44.33</t>
+        </is>
+      </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>22.06</t>
+        </is>
+      </c>
+      <c r="BA178" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AQ178" t="inlineStr">
-        <is>
-          <t>27.4</t>
-        </is>
-      </c>
-      <c r="AR178" t="inlineStr">
-        <is>
-          <t>84.52</t>
-        </is>
-      </c>
-      <c r="AS178" t="inlineStr">
-        <is>
-          <t>95.1609</t>
-        </is>
-      </c>
-      <c r="AT178" t="inlineStr">
-        <is>
-          <t>0.2571</t>
-        </is>
-      </c>
-      <c r="AU178" t="inlineStr">
-        <is>
-          <t>0.0391</t>
-        </is>
-      </c>
-      <c r="AV178" t="inlineStr">
-        <is>
-          <t>0.2498</t>
-        </is>
-      </c>
-      <c r="AW178" t="inlineStr">
-        <is>
-          <t>66.58</t>
-        </is>
-      </c>
-      <c r="AX178" t="inlineStr">
-        <is>
-          <t>0.96</t>
-        </is>
-      </c>
-      <c r="AY178" t="inlineStr">
-        <is>
-          <t>33.59</t>
-        </is>
-      </c>
-      <c r="AZ178" t="inlineStr">
-        <is>
-          <t>11.3</t>
-        </is>
-      </c>
-      <c r="BA178" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>0.0294</t>
+          <t>0.0777</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BD178" t="inlineStr">
         <is>
-          <t>37.64</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="BE178" t="inlineStr">
         <is>
-          <t>87.49</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="BF178" t="inlineStr">
         <is>
-          <t>0.3677</t>
+          <t>0.387</t>
         </is>
       </c>
       <c r="BG178" t="inlineStr">
         <is>
-          <t>0.1344</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="BH178" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="BI178" t="inlineStr">
         <is>
-          <t>214 deg</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BJ178" t="inlineStr">
@@ -57106,12 +57086,12 @@
       </c>
       <c r="BK178" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=40.4469&amp;lon=-80.0057</t>
         </is>
       </c>
       <c r="BL178" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>87</t>
         </is>
       </c>
       <c r="BM178" t="inlineStr">
@@ -57121,12 +57101,12 @@
       </c>
       <c r="BN178" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BO178" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BP178" t="inlineStr"/>
@@ -57147,47 +57127,47 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>669743</t>
+          <t>670032</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Alex Call</t>
+          <t>Nicky Lopez</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-08-15T23:15:00Z</t>
+          <t>2026-08-16T01:40:00Z</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>J.T. Ginn</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>669372</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -57196,7 +57176,7 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>29.2</v>
+        <v>30.1</v>
       </c>
       <c r="M179" t="inlineStr">
         <is>
@@ -57210,26 +57190,26 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P179" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="Q179" t="n">
-        <v>18.2</v>
+        <v>30.2</v>
       </c>
       <c r="R179" t="n">
-        <v>68.09999999999999</v>
+        <v>56.4</v>
       </c>
       <c r="S179" t="n">
-        <v>52.4</v>
+        <v>40.2</v>
       </c>
       <c r="T179" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U179" t="n">
-        <v>15.3</v>
+        <v>2</v>
       </c>
       <c r="V179" t="n">
         <v>50</v>
@@ -57237,35 +57217,39 @@
       <c r="W179" t="inlineStr"/>
       <c r="X179" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y179" t="inlineStr">
+      <c r="AB179" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA179" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AD179" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AD179" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AE179" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -57290,7 +57274,7 @@
       </c>
       <c r="AK179" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AL179" t="inlineStr">
@@ -57300,12 +57284,12 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/9, 0 HR</t>
+          <t>Last 7 games: 2/15, 0 HR</t>
         </is>
       </c>
       <c r="AN179" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.8% barrel, 11.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 14.2 HR allowed</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
@@ -57315,102 +57299,102 @@
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ179" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AR179" t="inlineStr">
         <is>
-          <t>85.33</t>
+          <t>84.52</t>
         </is>
       </c>
       <c r="AS179" t="inlineStr">
         <is>
-          <t>94.5569</t>
+          <t>95.1609</t>
         </is>
       </c>
       <c r="AT179" t="inlineStr">
         <is>
-          <t>0.2955</t>
+          <t>0.2571</t>
         </is>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>0.0784</t>
+          <t>0.0391</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>0.2888</t>
+          <t>0.2498</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>66.66</t>
+          <t>66.58</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>35.74</t>
+          <t>33.59</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>0.0907</t>
+          <t>0.0294</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BD179" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>37.64</t>
         </is>
       </c>
       <c r="BE179" t="inlineStr">
         <is>
-          <t>87.46</t>
+          <t>87.49</t>
         </is>
       </c>
       <c r="BF179" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>0.3677</t>
         </is>
       </c>
       <c r="BG179" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.1344</t>
         </is>
       </c>
       <c r="BH179" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="BI179" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>214 deg</t>
         </is>
       </c>
       <c r="BJ179" t="inlineStr">
@@ -57420,12 +57404,12 @@
       </c>
       <c r="BK179" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.5804&amp;lon=-121.5139</t>
         </is>
       </c>
       <c r="BL179" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>47</t>
         </is>
       </c>
       <c r="BM179" t="inlineStr">
@@ -57435,12 +57419,12 @@
       </c>
       <c r="BN179" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BO179" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BP179" t="inlineStr"/>
@@ -57461,27 +57445,27 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>669743</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Alex Call</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-08-15T23:10:00Z</t>
+          <t>2026-08-15T23:15:00Z</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -57491,26 +57475,26 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Wandy Peralta</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>593974</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="M180" t="inlineStr">
         <is>
@@ -57528,22 +57512,22 @@
         </is>
       </c>
       <c r="P180" t="n">
-        <v>9.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="Q180" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="R180" t="n">
-        <v>50.1</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="S180" t="n">
-        <v>44.8</v>
+        <v>52.4</v>
       </c>
       <c r="T180" t="n">
         <v>50</v>
       </c>
       <c r="U180" t="n">
-        <v>42</v>
+        <v>15.3</v>
       </c>
       <c r="V180" t="n">
         <v>50</v>
@@ -57561,7 +57545,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -57599,12 +57583,12 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AL180" t="inlineStr">
@@ -57614,117 +57598,117 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>Contact streak: 6/15 over last 7 games</t>
+          <t>Last 7 games: 2/9, 0 HR</t>
         </is>
       </c>
       <c r="AN180" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.6% barrel, 5.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.8% barrel, 11.5 HR allowed</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AQ180" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="AR180" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>85.33</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr">
         <is>
-          <t>93.5097</t>
+          <t>94.5569</t>
         </is>
       </c>
       <c r="AT180" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>0.2955</t>
         </is>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>0.0938</t>
+          <t>0.0784</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>0.2783</t>
+          <t>0.2888</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>66.66</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>35.74</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>35.22</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>0.0721</t>
+          <t>0.0907</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BD180" t="inlineStr">
         <is>
-          <t>33.96</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BE180" t="inlineStr">
         <is>
-          <t>87.04</t>
+          <t>87.46</t>
         </is>
       </c>
       <c r="BF180" t="inlineStr">
         <is>
-          <t>0.3759</t>
+          <t>0.274</t>
         </is>
       </c>
       <c r="BG180" t="inlineStr">
         <is>
-          <t>0.1169</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="BH180" t="inlineStr">
         <is>
-          <t>16.92</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="BI180" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ180" t="inlineStr">
@@ -57734,12 +57718,12 @@
       </c>
       <c r="BK180" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=41.4962&amp;lon=-81.6852</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=34.0739&amp;lon=-118.2400</t>
         </is>
       </c>
       <c r="BL180" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>62</t>
         </is>
       </c>
       <c r="BM180" t="inlineStr">
@@ -57749,12 +57733,12 @@
       </c>
       <c r="BN180" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BO180" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BP180" t="inlineStr"/>
@@ -57768,6 +57752,320 @@
       <c r="BX180" t="inlineStr"/>
       <c r="BY180" t="inlineStr"/>
       <c r="BZ180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>690984</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Petey Halpin</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-08-15T23:10:00Z</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Pre-Game</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Wandy Peralta</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>593974</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="L181" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>Watch List</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>No major boost</t>
+        </is>
+      </c>
+      <c r="P181" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="R181" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="S181" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="T181" t="n">
+        <v>50</v>
+      </c>
+      <c r="U181" t="n">
+        <v>42</v>
+      </c>
+      <c r="V181" t="n">
+        <v>50</v>
+      </c>
+      <c r="W181" t="inlineStr"/>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD181" t="inlineStr"/>
+      <c r="AE181" t="inlineStr">
+        <is>
+          <t>H:2026/2025 P:2026/2025</t>
+        </is>
+      </c>
+      <c r="AF181" t="inlineStr"/>
+      <c r="AG181" t="inlineStr"/>
+      <c r="AH181" t="inlineStr">
+        <is>
+          <t>Direct BvP not yet weighted; 2026/2025 Statcast baseline active</t>
+        </is>
+      </c>
+      <c r="AI181" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AJ181" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AK181" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AL181" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM181" t="inlineStr">
+        <is>
+          <t>Contact streak: 6/15 over last 7 games</t>
+        </is>
+      </c>
+      <c r="AN181" t="inlineStr">
+        <is>
+          <t>same-side matchup; pitcher baseline 4.6% barrel, 5.0 HR allowed</t>
+        </is>
+      </c>
+      <c r="AO181" t="inlineStr">
+        <is>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AP181" t="inlineStr">
+        <is>
+          <t>5.11</t>
+        </is>
+      </c>
+      <c r="AQ181" t="inlineStr">
+        <is>
+          <t>18.2</t>
+        </is>
+      </c>
+      <c r="AR181" t="inlineStr">
+        <is>
+          <t>81.45</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr">
+        <is>
+          <t>93.5097</t>
+        </is>
+      </c>
+      <c r="AT181" t="inlineStr">
+        <is>
+          <t>0.308</t>
+        </is>
+      </c>
+      <c r="AU181" t="inlineStr">
+        <is>
+          <t>0.0938</t>
+        </is>
+      </c>
+      <c r="AV181" t="inlineStr">
+        <is>
+          <t>0.2783</t>
+        </is>
+      </c>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>70.22</t>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>5.81</t>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr">
+        <is>
+          <t>39.78</t>
+        </is>
+      </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>35.22</t>
+        </is>
+      </c>
+      <c r="BA181" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="BB181" t="inlineStr">
+        <is>
+          <t>0.0721</t>
+        </is>
+      </c>
+      <c r="BC181" t="inlineStr">
+        <is>
+          <t>4.59</t>
+        </is>
+      </c>
+      <c r="BD181" t="inlineStr">
+        <is>
+          <t>33.96</t>
+        </is>
+      </c>
+      <c r="BE181" t="inlineStr">
+        <is>
+          <t>87.04</t>
+        </is>
+      </c>
+      <c r="BF181" t="inlineStr">
+        <is>
+          <t>0.3759</t>
+        </is>
+      </c>
+      <c r="BG181" t="inlineStr">
+        <is>
+          <t>0.1169</t>
+        </is>
+      </c>
+      <c r="BH181" t="inlineStr">
+        <is>
+          <t>16.92</t>
+        </is>
+      </c>
+      <c r="BI181" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BJ181" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK181" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=41.4962&amp;lon=-81.6852</t>
+        </is>
+      </c>
+      <c r="BL181" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="BM181" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN181" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="BO181" t="inlineStr">
+        <is>
+          <t>Progressive Field</t>
+        </is>
+      </c>
+      <c r="BP181" t="inlineStr"/>
+      <c r="BQ181" t="inlineStr"/>
+      <c r="BR181" t="inlineStr"/>
+      <c r="BS181" t="inlineStr"/>
+      <c r="BT181" t="inlineStr"/>
+      <c r="BU181" t="inlineStr"/>
+      <c r="BV181" t="inlineStr"/>
+      <c r="BW181" t="inlineStr"/>
+      <c r="BX181" t="inlineStr"/>
+      <c r="BY181" t="inlineStr"/>
+      <c r="BZ181" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -61494,28 +61792,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -62124,34 +62426,30 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -64014,28 +64312,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
